--- a/business-libraries/test-data/student_case/keyword_route.xlsx
+++ b/business-libraries/test-data/student_case/keyword_route.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -448,16 +448,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>KW_ST_01</v>
+        <v>SC_KW_01</v>
       </c>
       <c r="B2" t="str">
-        <v>不想活</v>
+        <v>不想活,想死,活着没意思</v>
       </c>
       <c r="C2" t="str">
-        <v>不想活相关；工作压力大；感觉疲惫</v>
+        <v>结束生命,生无可恋,不如死了</v>
       </c>
       <c r="D2" t="str">
-        <v>开玩笑的表达；反讽</v>
+        <v>不想活了（玩笑）</v>
       </c>
       <c r="E2" t="str">
         <v>student_case</v>
@@ -472,36 +472,36 @@
         <v>red</v>
       </c>
       <c r="I2" t="str">
-        <v>不想活</v>
+        <v>自杀意念</v>
       </c>
       <c r="J2" t="str">
-        <v>ST_FIVE_Q</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="K2" t="str">
-        <v>ST_RX_001</v>
+        <v>SC_RX_006</v>
       </c>
       <c r="L2" t="str">
-        <v>未触发红线</v>
+        <v/>
       </c>
       <c r="M2" t="str">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="str">
         <v>always</v>
       </c>
       <c r="O2" t="str">
-        <v>教师在对话中表达不想活相关信号，触发学生个体问题模块评估和工具推荐</v>
+        <v>任一命中即走危机流程，不分时段和模块</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>KW_ST_02</v>
+        <v>SC_KW_02</v>
       </c>
       <c r="B3" t="str">
-        <v>学生自伤</v>
+        <v>自伤,划手,伤害自己</v>
       </c>
       <c r="C3" t="str">
-        <v>学生自伤相关；学生自伤表现</v>
+        <v>割腕,弄伤自己</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -510,45 +510,45 @@
         <v>student_case</v>
       </c>
       <c r="F3" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" t="str">
-        <v>fuzzy</v>
+        <v>exact</v>
       </c>
       <c r="H3" t="str">
-        <v>orange</v>
+        <v>red</v>
       </c>
       <c r="I3" t="str">
-        <v>学生自伤</v>
+        <v>自伤行为</v>
       </c>
       <c r="J3" t="str">
-        <v>ST_FIVE_Q</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="K3" t="str">
-        <v>ST_RX_002</v>
+        <v>SC_RX_006</v>
       </c>
       <c r="L3" t="str">
         <v/>
       </c>
       <c r="M3" t="str">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N3" t="str">
         <v>always</v>
       </c>
       <c r="O3" t="str">
-        <v>教师表达学生自伤相关困扰，推荐对应自我照顾工具</v>
+        <v>自伤相关表达，立即走危机流程</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>KW_ST_03</v>
+        <v>SC_KW_03</v>
       </c>
       <c r="B4" t="str">
-        <v>校园欺凌</v>
+        <v>不想上学,不肯来,请假很多</v>
       </c>
       <c r="C4" t="str">
-        <v>校园欺凌相关；情绪不良</v>
+        <v>拒学,逃学,装病</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -557,45 +557,45 @@
         <v>student_case</v>
       </c>
       <c r="F4" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G4" t="str">
         <v>fuzzy</v>
       </c>
       <c r="H4" t="str">
-        <v>yellow</v>
+        <v>orange</v>
       </c>
       <c r="I4" t="str">
-        <v>校园欺凌</v>
+        <v>拒学信号</v>
       </c>
       <c r="J4" t="str">
-        <v>ST_QUICK</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="K4" t="str">
-        <v>ST_RX_003</v>
+        <v>SC_RX_004</v>
       </c>
       <c r="L4" t="str">
-        <v>未触发红线</v>
+        <v/>
       </c>
       <c r="M4" t="str">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="N4" t="str">
         <v>always</v>
       </c>
       <c r="O4" t="str">
-        <v>教师表达校园欺凌相关信号，推荐同伴支持或自评</v>
+        <v>出现拒学相关信号</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>KW_ST_04</v>
+        <v>SC_KW_04</v>
       </c>
       <c r="B5" t="str">
-        <v>厌学</v>
+        <v>被欺负,被孤立,没人跟他玩</v>
       </c>
       <c r="C5" t="str">
-        <v>厌学相关；无精打采</v>
+        <v>被排挤,被针对</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -604,39 +604,86 @@
         <v>student_case</v>
       </c>
       <c r="F5" t="str">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G5" t="str">
         <v>fuzzy</v>
       </c>
       <c r="H5" t="str">
-        <v>yellow</v>
+        <v>orange</v>
       </c>
       <c r="I5" t="str">
-        <v>厌学</v>
+        <v>同伴排斥</v>
       </c>
       <c r="J5" t="str">
-        <v>ST_QUICK</v>
+        <v>SC_EBRCA</v>
       </c>
       <c r="K5" t="str">
-        <v>ST_RX_004</v>
+        <v>SC_RX_003</v>
       </c>
       <c r="L5" t="str">
         <v/>
       </c>
       <c r="M5" t="str">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="N5" t="str">
         <v>always</v>
       </c>
       <c r="O5" t="str">
-        <v>教师表达厌学相关信号，推荐认知类工具</v>
+        <v>出现同伴排斥信号</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>SC_KW_05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>情绪不好,很低落,爱哭</v>
+      </c>
+      <c r="C6" t="str">
+        <v>不说话,躲着人,发脾气</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="F6" t="str">
+        <v>5</v>
+      </c>
+      <c r="G6" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H6" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I6" t="str">
+        <v>情绪信号</v>
+      </c>
+      <c r="J6" t="str">
+        <v>SC_FIVE_CAT</v>
+      </c>
+      <c r="K6" t="str">
+        <v>SC_RX_002</v>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v>0.7</v>
+      </c>
+      <c r="N6" t="str">
+        <v>always</v>
+      </c>
+      <c r="O6" t="str">
+        <v>出现情绪相关信号</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/student_case/keyword_route.xlsx
+++ b/business-libraries/test-data/student_case/keyword_route.xlsx
@@ -451,10 +451,10 @@
         <v>SC_KW_01</v>
       </c>
       <c r="B2" t="str">
-        <v>不想活,想死,活着没意思</v>
+        <v>不想活;想死;活着没意思</v>
       </c>
       <c r="C2" t="str">
-        <v>结束生命,生无可恋,不如死了</v>
+        <v>结束生命;生无可恋;不如死了</v>
       </c>
       <c r="D2" t="str">
         <v>不想活了（玩笑）</v>
@@ -475,16 +475,16 @@
         <v>自杀意念</v>
       </c>
       <c r="J2" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="K2" t="str">
-        <v>SC_RX_006</v>
+        <v>SC_RX_06</v>
       </c>
       <c r="L2" t="str">
         <v/>
       </c>
       <c r="M2" t="str">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="N2" t="str">
         <v>always</v>
@@ -498,10 +498,10 @@
         <v>SC_KW_02</v>
       </c>
       <c r="B3" t="str">
-        <v>自伤,划手,伤害自己</v>
+        <v>自伤;划手;伤害自己</v>
       </c>
       <c r="C3" t="str">
-        <v>割腕,弄伤自己</v>
+        <v>割腕;弄伤自己</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -522,16 +522,16 @@
         <v>自伤行为</v>
       </c>
       <c r="J3" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="K3" t="str">
-        <v>SC_RX_006</v>
+        <v>SC_RX_06</v>
       </c>
       <c r="L3" t="str">
         <v/>
       </c>
       <c r="M3" t="str">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="N3" t="str">
         <v>always</v>
@@ -545,10 +545,10 @@
         <v>SC_KW_03</v>
       </c>
       <c r="B4" t="str">
-        <v>不想上学,不肯来,请假很多</v>
+        <v>不想上学;不肯来;请假很多</v>
       </c>
       <c r="C4" t="str">
-        <v>拒学,逃学,装病</v>
+        <v>拒学;逃学;装病</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -569,16 +569,16 @@
         <v>拒学信号</v>
       </c>
       <c r="J4" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="K4" t="str">
-        <v>SC_RX_004</v>
+        <v>SC_RX_04</v>
       </c>
       <c r="L4" t="str">
         <v/>
       </c>
       <c r="M4" t="str">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="N4" t="str">
         <v>always</v>
@@ -592,10 +592,10 @@
         <v>SC_KW_04</v>
       </c>
       <c r="B5" t="str">
-        <v>被欺负,被孤立,没人跟他玩</v>
+        <v>被欺负;被孤立;没人跟他玩</v>
       </c>
       <c r="C5" t="str">
-        <v>被排挤,被针对</v>
+        <v>被排挤;被针对</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -616,16 +616,16 @@
         <v>同伴排斥</v>
       </c>
       <c r="J5" t="str">
-        <v>SC_EBRCA</v>
+        <v>SC_S2</v>
       </c>
       <c r="K5" t="str">
-        <v>SC_RX_003</v>
+        <v>SC_RX_03</v>
       </c>
       <c r="L5" t="str">
         <v/>
       </c>
       <c r="M5" t="str">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="N5" t="str">
         <v>always</v>
@@ -639,10 +639,10 @@
         <v>SC_KW_05</v>
       </c>
       <c r="B6" t="str">
-        <v>情绪不好,很低落,爱哭</v>
+        <v>情绪不好;很低落;爱哭</v>
       </c>
       <c r="C6" t="str">
-        <v>不说话,躲着人,发脾气</v>
+        <v>不说话;躲着人;发脾气</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -663,16 +663,16 @@
         <v>情绪信号</v>
       </c>
       <c r="J6" t="str">
-        <v>SC_FIVE_CAT</v>
+        <v>SC_S1</v>
       </c>
       <c r="K6" t="str">
-        <v>SC_RX_002</v>
+        <v>SC_RX_02</v>
       </c>
       <c r="L6" t="str">
         <v/>
       </c>
       <c r="M6" t="str">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="N6" t="str">
         <v>always</v>

--- a/business-libraries/test-data/student_case/keyword_route.xlsx
+++ b/business-libraries/test-data/student_case/keyword_route.xlsx
@@ -451,10 +451,10 @@
         <v>SC_KW_01</v>
       </c>
       <c r="B2" t="str">
-        <v>不想活;想死;活着没意思</v>
+        <v>不想活,想死,活着没意思</v>
       </c>
       <c r="C2" t="str">
-        <v>结束生命;生无可恋;不如死了</v>
+        <v>结束生命,生无可恋,不如死了</v>
       </c>
       <c r="D2" t="str">
         <v>不想活了（玩笑）</v>
@@ -475,16 +475,16 @@
         <v>自杀意念</v>
       </c>
       <c r="J2" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="K2" t="str">
-        <v>SC_RX_06</v>
+        <v>SC_RX_006</v>
       </c>
       <c r="L2" t="str">
         <v/>
       </c>
       <c r="M2" t="str">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N2" t="str">
         <v>always</v>
@@ -498,10 +498,10 @@
         <v>SC_KW_02</v>
       </c>
       <c r="B3" t="str">
-        <v>自伤;划手;伤害自己</v>
+        <v>自伤,划手,伤害自己</v>
       </c>
       <c r="C3" t="str">
-        <v>割腕;弄伤自己</v>
+        <v>割腕,弄伤自己</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -522,16 +522,16 @@
         <v>自伤行为</v>
       </c>
       <c r="J3" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="K3" t="str">
-        <v>SC_RX_06</v>
+        <v>SC_RX_006</v>
       </c>
       <c r="L3" t="str">
         <v/>
       </c>
       <c r="M3" t="str">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N3" t="str">
         <v>always</v>
@@ -545,10 +545,10 @@
         <v>SC_KW_03</v>
       </c>
       <c r="B4" t="str">
-        <v>不想上学;不肯来;请假很多</v>
+        <v>不想上学,不肯来,请假很多</v>
       </c>
       <c r="C4" t="str">
-        <v>拒学;逃学;装病</v>
+        <v>拒学,逃学,装病</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -569,16 +569,16 @@
         <v>拒学信号</v>
       </c>
       <c r="J4" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="K4" t="str">
-        <v>SC_RX_04</v>
+        <v>SC_RX_004</v>
       </c>
       <c r="L4" t="str">
         <v/>
       </c>
       <c r="M4" t="str">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N4" t="str">
         <v>always</v>
@@ -592,10 +592,10 @@
         <v>SC_KW_04</v>
       </c>
       <c r="B5" t="str">
-        <v>被欺负;被孤立;没人跟他玩</v>
+        <v>被欺负,被孤立,没人跟他玩</v>
       </c>
       <c r="C5" t="str">
-        <v>被排挤;被针对</v>
+        <v>被排挤,被针对</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -616,16 +616,16 @@
         <v>同伴排斥</v>
       </c>
       <c r="J5" t="str">
-        <v>SC_S2</v>
+        <v>SC_EBRCA</v>
       </c>
       <c r="K5" t="str">
-        <v>SC_RX_03</v>
+        <v>SC_RX_003</v>
       </c>
       <c r="L5" t="str">
         <v/>
       </c>
       <c r="M5" t="str">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="N5" t="str">
         <v>always</v>
@@ -639,10 +639,10 @@
         <v>SC_KW_05</v>
       </c>
       <c r="B6" t="str">
-        <v>情绪不好;很低落;爱哭</v>
+        <v>情绪不好,很低落,爱哭</v>
       </c>
       <c r="C6" t="str">
-        <v>不说话;躲着人;发脾气</v>
+        <v>不说话,躲着人,发脾气</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -663,16 +663,16 @@
         <v>情绪信号</v>
       </c>
       <c r="J6" t="str">
-        <v>SC_S1</v>
+        <v>SC_FIVE_CAT</v>
       </c>
       <c r="K6" t="str">
-        <v>SC_RX_02</v>
+        <v>SC_RX_002</v>
       </c>
       <c r="L6" t="str">
         <v/>
       </c>
       <c r="M6" t="str">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="N6" t="str">
         <v>always</v>

--- a/business-libraries/test-data/student_case/keyword_route.xlsx
+++ b/business-libraries/test-data/student_case/keyword_route.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -451,13 +451,13 @@
         <v>SC_KW_01</v>
       </c>
       <c r="B2" t="str">
-        <v>不想活;想死;活着没意思</v>
+        <v>自杀;自伤;不想活;死了算了;割;跳楼;跳河;消失;结束</v>
       </c>
       <c r="C2" t="str">
-        <v>结束生命;生无可恋;不如死了</v>
+        <v>结束生命;生无可恋;不如死了;割腕;不想活了</v>
       </c>
       <c r="D2" t="str">
-        <v>不想活了（玩笑）</v>
+        <v/>
       </c>
       <c r="E2" t="str">
         <v>student_case</v>
@@ -472,13 +472,13 @@
         <v>red</v>
       </c>
       <c r="I2" t="str">
-        <v>自杀意念</v>
+        <v>安全红线·自杀自伤</v>
       </c>
       <c r="J2" t="str">
         <v>SC_S1</v>
       </c>
       <c r="K2" t="str">
-        <v>SC_RX_06</v>
+        <v>SC_RX_18</v>
       </c>
       <c r="L2" t="str">
         <v/>
@@ -490,7 +490,7 @@
         <v>always</v>
       </c>
       <c r="O2" t="str">
-        <v>任一命中即走危机流程，不分时段和模块</v>
+        <v>SA01：学生表现出或表达出自杀意念、自伤行为、死亡愿望或自我毁灭倾向；题1≥4 或谈话/作文/绘画中直接或间接表达→红色(L5)立即响应：不让学生独处、通知心理总监和校领导、通知家长、24 小时内安全计划确认</v>
       </c>
     </row>
     <row r="3">
@@ -498,10 +498,10 @@
         <v>SC_KW_02</v>
       </c>
       <c r="B3" t="str">
-        <v>自伤;划手;伤害自己</v>
+        <v>打;杀;捅;揍;报复;武器;刀;爆炸;攻击</v>
       </c>
       <c r="C3" t="str">
-        <v>割腕;弄伤自己</v>
+        <v>打死;杀了;弄死;打人;报复他</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -519,13 +519,13 @@
         <v>red</v>
       </c>
       <c r="I3" t="str">
-        <v>自伤行为</v>
+        <v>安全红线·严重攻击</v>
       </c>
       <c r="J3" t="str">
         <v>SC_S1</v>
       </c>
       <c r="K3" t="str">
-        <v>SC_RX_06</v>
+        <v>SC_RX_18</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -537,7 +537,7 @@
         <v>always</v>
       </c>
       <c r="O3" t="str">
-        <v>自伤相关表达，立即走危机流程</v>
+        <v>SA02：学生表现出或表达出对他人的严重攻击意图、暴力行为或持械威胁；题7≥4 或 B3 激活且 SSF≥0.7→红色(L5)：立即隔离保护、联系家长必要时报警、心理总监评估攻击风险</v>
       </c>
     </row>
     <row r="4">
@@ -545,10 +545,10 @@
         <v>SC_KW_03</v>
       </c>
       <c r="B4" t="str">
-        <v>不想上学;不肯来;请假很多</v>
+        <v>体罚;抽;关;不给饭吃;不让睡觉;锁;淤青;恐惧回家;伤</v>
       </c>
       <c r="C4" t="str">
-        <v>拒学;逃学;装病</v>
+        <v>被打了;回家害怕;身上有伤</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -560,19 +560,19 @@
         <v>3</v>
       </c>
       <c r="G4" t="str">
-        <v>fuzzy</v>
+        <v>exact</v>
       </c>
       <c r="H4" t="str">
-        <v>orange</v>
+        <v>red</v>
       </c>
       <c r="I4" t="str">
-        <v>拒学信号</v>
+        <v>安全红线·虐待忽视</v>
       </c>
       <c r="J4" t="str">
         <v>SC_S1</v>
       </c>
       <c r="K4" t="str">
-        <v>SC_RX_04</v>
+        <v>SC_RX_01</v>
       </c>
       <c r="L4" t="str">
         <v/>
@@ -584,7 +584,7 @@
         <v>always</v>
       </c>
       <c r="O4" t="str">
-        <v>出现拒学相关信号</v>
+        <v>SA03：学生身上存在体罚、言语羞辱、基本生活照料缺失或性侵害迹象；题1/题15 触发或身体出现不明伤痕→红色(L5)：记录具体信号、通过学校正式渠道启动未成年人保护流程、联系心理总监安全评估</v>
       </c>
     </row>
     <row r="5">
@@ -592,10 +592,10 @@
         <v>SC_KW_04</v>
       </c>
       <c r="B5" t="str">
-        <v>被欺负;被孤立;没人跟他玩</v>
+        <v>幻觉;幻听;感觉被监视;完全不吃不睡</v>
       </c>
       <c r="C5" t="str">
-        <v>被排挤;被针对</v>
+        <v>听到奇怪的声音;觉得有人要害他</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -607,19 +607,19 @@
         <v>4</v>
       </c>
       <c r="G5" t="str">
-        <v>fuzzy</v>
+        <v>exact</v>
       </c>
       <c r="H5" t="str">
-        <v>orange</v>
+        <v>red</v>
       </c>
       <c r="I5" t="str">
-        <v>同伴排斥</v>
+        <v>安全红线·心理健康高危</v>
       </c>
       <c r="J5" t="str">
-        <v>SC_S2</v>
+        <v>SC_S1</v>
       </c>
       <c r="K5" t="str">
-        <v>SC_RX_03</v>
+        <v>SC_RX_01</v>
       </c>
       <c r="L5" t="str">
         <v/>
@@ -631,7 +631,7 @@
         <v>always</v>
       </c>
       <c r="O5" t="str">
-        <v>出现同伴排斥信号</v>
+        <v>SA04：E2 编码激活或 SAFETY 维度≥4，学生可能出现严重心理障碍急性表现→红色(L5)：立即上报警报、心理总监评估是否需要精神科转介、家校联动启动保护计划、升级为全校级关注</v>
       </c>
     </row>
     <row r="6">
@@ -639,10 +639,10 @@
         <v>SC_KW_05</v>
       </c>
       <c r="B6" t="str">
-        <v>情绪不好;很低落;爱哭</v>
+        <v>失控;号啕大哭;尖叫;摔东西;自伤;完全无法正常对话;眼神空洞</v>
       </c>
       <c r="C6" t="str">
-        <v>不说话;躲着人;发脾气</v>
+        <v>情绪崩溃;大哭不止</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -654,19 +654,19 @@
         <v>5</v>
       </c>
       <c r="G6" t="str">
-        <v>fuzzy</v>
+        <v>exact</v>
       </c>
       <c r="H6" t="str">
-        <v>yellow</v>
+        <v>orange</v>
       </c>
       <c r="I6" t="str">
-        <v>情绪信号</v>
+        <v>安全红线·急性情绪崩溃</v>
       </c>
       <c r="J6" t="str">
         <v>SC_S1</v>
       </c>
       <c r="K6" t="str">
-        <v>SC_RX_02</v>
+        <v>SC_RX_18</v>
       </c>
       <c r="L6" t="str">
         <v/>
@@ -678,12 +678,106 @@
         <v>always</v>
       </c>
       <c r="O6" t="str">
-        <v>出现情绪相关信号</v>
+        <v>SA05：在校期间失控哭泣、尖叫、自我伤害或完全无法沟通的急性情绪危机；C2 激活且 SSF≥0.7 或失控&gt;10 分钟→橙转红(L4→L5)：带离公共空间、一人陪护不围观、T12 不撑不退、平复不了联系家长和心理教师</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>SC_KW_06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>打人;砸东西;掀桌子;扔椅子;冲出去;对老师动手;完全不听任何指令</v>
+      </c>
+      <c r="C7" t="str">
+        <v>破坏课堂;扰乱课堂</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="F7" t="str">
+        <v>6</v>
+      </c>
+      <c r="G7" t="str">
+        <v>exact</v>
+      </c>
+      <c r="H7" t="str">
+        <v>orange</v>
+      </c>
+      <c r="I7" t="str">
+        <v>安全红线·扰乱秩序</v>
+      </c>
+      <c r="J7" t="str">
+        <v>SC_S1</v>
+      </c>
+      <c r="K7" t="str">
+        <v>SC_RX_03</v>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N7" t="str">
+        <v>always</v>
+      </c>
+      <c r="O7" t="str">
+        <v>SA06：行为严重破坏课堂秩序，常规课堂管理完全失效，班级安全受威胁；B3 激活且行为升级或破坏行为持续 15 分钟以上→橙色(L4)升级评估：联系安保带离、通知家长到校、心理教师当天介入评估</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>SC_KW_07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>不上学;不进班;完全沉默;寸步不离;反复确认;老师不在就崩溃;攻击;后悔;讨好</v>
+      </c>
+      <c r="C8" t="str">
+        <v>不去学校;不肯进教室;黏着老师</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="F8" t="str">
+        <v>7</v>
+      </c>
+      <c r="G8" t="str">
+        <v>exact</v>
+      </c>
+      <c r="H8" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I8" t="str">
+        <v>安全红线·依恋危机</v>
+      </c>
+      <c r="J8" t="str">
+        <v>SC_S1</v>
+      </c>
+      <c r="K8" t="str">
+        <v>SC_RX_31</v>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N8" t="str">
+        <v>always</v>
+      </c>
+      <c r="O8" t="str">
+        <v>SA07：不安全依恋学生的依恋需求被严重触发——回避型突然拒绝上学/焦虑型过度黏着/混乱型攻击-躲避交替→黄转橙(L3→L4)：先稳定关系用 T12 不撑不退、不在此阶段施加学业行为要求、以「了解近期变化」而非「告状」方式通知家长、启动依恋关系修复计划</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O8"/>
   </ignoredErrors>
 </worksheet>
 </file>